--- a/MavenBook/src/test/resources/PurchaseOrderData.xlsx
+++ b/MavenBook/src/test/resources/PurchaseOrderData.xlsx
@@ -4,18 +4,18 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11970" windowHeight="495"/>
   </bookViews>
   <sheets>
     <sheet name="PurchaseOrderHeader" sheetId="1" r:id="rId1"/>
     <sheet name="PurchaseOrderItems" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
   <si>
     <t>Reference Number</t>
   </si>
@@ -38,32 +38,98 @@
     <t>Vendor Name</t>
   </si>
   <si>
-    <t>ReTest20</t>
-  </si>
-  <si>
     <t>Purchase Order Date</t>
   </si>
   <si>
-    <t>Red Pen</t>
-  </si>
-  <si>
-    <t>Banana</t>
-  </si>
-  <si>
-    <t>231225-1</t>
-  </si>
-  <si>
-    <t>24-12-2025</t>
-  </si>
-  <si>
-    <t>30-12-2025</t>
+    <t>Tax</t>
+  </si>
+  <si>
+    <t>Customer Notes</t>
+  </si>
+  <si>
+    <t>Terms And Conditions</t>
+  </si>
+  <si>
+    <t>Save As</t>
+  </si>
+  <si>
+    <t>Price List</t>
+  </si>
+  <si>
+    <t>notex</t>
+  </si>
+  <si>
+    <t>termsx</t>
+  </si>
+  <si>
+    <t>Discount Level</t>
+  </si>
+  <si>
+    <t>Discount Type</t>
+  </si>
+  <si>
+    <t>Discount</t>
+  </si>
+  <si>
+    <t>Discount Account</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>Purchase Discount</t>
+  </si>
+  <si>
+    <t>Discount TType</t>
+  </si>
+  <si>
+    <t>DiscountT</t>
+  </si>
+  <si>
+    <t>Discount After-Before Tax</t>
+  </si>
+  <si>
+    <t>Before Tax</t>
+  </si>
+  <si>
+    <t>SAVE AND SUBMIT</t>
+  </si>
+  <si>
+    <t>Exclusive</t>
+  </si>
+  <si>
+    <t>UAE Vendor</t>
+  </si>
+  <si>
+    <t>25-05-2026</t>
+  </si>
+  <si>
+    <t>13426-1</t>
+  </si>
+  <si>
+    <t>At transaction level</t>
+  </si>
+  <si>
+    <t>Notebook 100</t>
+  </si>
+  <si>
+    <t>Pencils 10</t>
+  </si>
+  <si>
+    <t>Desk Note</t>
+  </si>
+  <si>
+    <t>Coffe</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -87,6 +153,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -96,7 +173,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -104,11 +181,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -131,6 +223,21 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -435,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.28515625" style="2" customWidth="1"/>
@@ -443,9 +550,18 @@
     <col min="3" max="3" width="21.42578125" style="2" customWidth="1"/>
     <col min="4" max="4" width="16.28515625" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="8" width="25.7109375" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="17.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.42578125" customWidth="1"/>
+    <col min="13" max="13" width="23" customWidth="1"/>
+    <col min="14" max="14" width="22.7109375" customWidth="1"/>
+    <col min="15" max="15" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -453,7 +569,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>3</v>
@@ -461,92 +577,331 @@
       <c r="E1" s="9" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>7</v>
+      <c r="F1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>12</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C2" s="7"/>
       <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2">
+        <v>10</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="M2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="7"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="12"/>
       <c r="C3" s="7"/>
       <c r="D3" s="6"/>
       <c r="E3" s="7"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C4" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="7"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="12"/>
       <c r="D4" s="6"/>
       <c r="E4" s="7"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C5" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="11"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="12"/>
       <c r="D5" s="6"/>
       <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="11"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="12"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="11"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="12"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="C6:C14" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" style="2" customWidth="1"/>
     <col min="2" max="2" width="15.5703125" customWidth="1"/>
     <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="D1" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="16">
+        <v>5</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="16">
         <v>10</v>
       </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="16">
+        <v>5</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="16">
+        <v>5</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="16">
+        <v>5</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="17"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="17"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="17"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="17"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="17"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="18"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="18"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="18"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="18"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="18"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="18"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="18"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/MavenBook/src/test/resources/PurchaseOrderData.xlsx
+++ b/MavenBook/src/test/resources/PurchaseOrderData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <t>Reference Number</t>
   </si>
@@ -77,9 +77,6 @@
     <t>%</t>
   </si>
   <si>
-    <t>amount</t>
-  </si>
-  <si>
     <t>Purchase Discount</t>
   </si>
   <si>
@@ -95,15 +92,9 @@
     <t>Before Tax</t>
   </si>
   <si>
-    <t>SAVE AND SUBMIT</t>
-  </si>
-  <si>
     <t>Exclusive</t>
   </si>
   <si>
-    <t>UAE Vendor</t>
-  </si>
-  <si>
     <t>25-05-2026</t>
   </si>
   <si>
@@ -113,16 +104,13 @@
     <t>At transaction level</t>
   </si>
   <si>
-    <t>Notebook 100</t>
-  </si>
-  <si>
-    <t>Pencils 10</t>
-  </si>
-  <si>
-    <t>Desk Note</t>
-  </si>
-  <si>
-    <t>Coffe</t>
+    <t>Thomas</t>
+  </si>
+  <si>
+    <t>SAVE AND APPROVE</t>
+  </si>
+  <si>
+    <t>Pear</t>
   </si>
 </sst>
 </file>
@@ -584,13 +572,13 @@
         <v>15</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I1" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="K1" s="10" t="s">
         <v>18</v>
@@ -610,35 +598,35 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
         <v>19</v>
       </c>
       <c r="J2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L2" s="7" t="s">
         <v>13</v>
@@ -647,7 +635,7 @@
         <v>14</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="O2" s="7"/>
     </row>
@@ -750,71 +738,37 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" s="16">
-        <v>5</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="16">
-        <v>10</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="16">
-        <v>5</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="16">
-        <v>10</v>
-      </c>
+      <c r="A3" s="12"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="16">
-        <v>5</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="16">
-        <v>10</v>
-      </c>
+      <c r="A4" s="12"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="16">
-        <v>5</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="16">
-        <v>10</v>
-      </c>
+      <c r="A5" s="12"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>

--- a/MavenBook/src/test/resources/PurchaseOrderData.xlsx
+++ b/MavenBook/src/test/resources/PurchaseOrderData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11970" windowHeight="495"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11970" windowHeight="495" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="PurchaseOrderHeader" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="95">
   <si>
     <t>Reference Number</t>
   </si>
@@ -29,9 +29,6 @@
     <t>Payment Terms</t>
   </si>
   <si>
-    <t>Net 15</t>
-  </si>
-  <si>
     <t>Exp delivery Date</t>
   </si>
   <si>
@@ -77,6 +74,9 @@
     <t>%</t>
   </si>
   <si>
+    <t>amount</t>
+  </si>
+  <si>
     <t>Purchase Discount</t>
   </si>
   <si>
@@ -92,32 +92,221 @@
     <t>Before Tax</t>
   </si>
   <si>
+    <t>SAVE AND SUBMIT</t>
+  </si>
+  <si>
     <t>Exclusive</t>
   </si>
   <si>
-    <t>25-05-2026</t>
-  </si>
-  <si>
-    <t>13426-1</t>
+    <t>Service 1</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>Orange</t>
+  </si>
+  <si>
+    <t>VAT Reg Vendor</t>
   </si>
   <si>
     <t>At transaction level</t>
   </si>
   <si>
-    <t>Thomas</t>
+    <t>Non Vat Vendor</t>
+  </si>
+  <si>
+    <t>GCC Vat Reg Oman</t>
+  </si>
+  <si>
+    <t>GCC Non Vat Oman</t>
+  </si>
+  <si>
+    <t>None GCC V</t>
+  </si>
+  <si>
+    <t>10082026-1</t>
+  </si>
+  <si>
+    <t>10082026-2</t>
+  </si>
+  <si>
+    <t>10082026-3</t>
+  </si>
+  <si>
+    <t>10082026-4</t>
+  </si>
+  <si>
+    <t>10082026-5</t>
+  </si>
+  <si>
+    <t>10082026-6</t>
+  </si>
+  <si>
+    <t>10082026-7</t>
+  </si>
+  <si>
+    <t>10082026-8</t>
+  </si>
+  <si>
+    <t>10082026-9</t>
+  </si>
+  <si>
+    <t>10082026-10</t>
+  </si>
+  <si>
+    <t>10082026-11</t>
+  </si>
+  <si>
+    <t>10082026-12</t>
+  </si>
+  <si>
+    <t>10082026-13</t>
+  </si>
+  <si>
+    <t>10082026-14</t>
+  </si>
+  <si>
+    <t>10082026-15</t>
+  </si>
+  <si>
+    <t>10082026-16</t>
+  </si>
+  <si>
+    <t>10082026-17</t>
+  </si>
+  <si>
+    <t>10082026-18</t>
+  </si>
+  <si>
+    <t>10082026-19</t>
+  </si>
+  <si>
+    <t>10082026-20</t>
+  </si>
+  <si>
+    <t>10082026-21</t>
+  </si>
+  <si>
+    <t>10082026-22</t>
+  </si>
+  <si>
+    <t>10082026-23</t>
+  </si>
+  <si>
+    <t>10082026-24</t>
+  </si>
+  <si>
+    <t>10082026-25</t>
+  </si>
+  <si>
+    <t>10082026-26</t>
+  </si>
+  <si>
+    <t>10082026-27</t>
+  </si>
+  <si>
+    <t>10082026-28</t>
+  </si>
+  <si>
+    <t>10082026-29</t>
+  </si>
+  <si>
+    <t>10082026-30</t>
+  </si>
+  <si>
+    <t>10082026-31</t>
+  </si>
+  <si>
+    <t>10082026-32</t>
+  </si>
+  <si>
+    <t>10082026-33</t>
+  </si>
+  <si>
+    <t>10082026-34</t>
+  </si>
+  <si>
+    <t>10082026-35</t>
+  </si>
+  <si>
+    <t>10082026-36</t>
+  </si>
+  <si>
+    <t>10082026-37</t>
+  </si>
+  <si>
+    <t>10082026-38</t>
+  </si>
+  <si>
+    <t>10082026-39</t>
+  </si>
+  <si>
+    <t>10082026-40</t>
+  </si>
+  <si>
+    <t>10082026-41</t>
+  </si>
+  <si>
+    <t>10082026-42</t>
+  </si>
+  <si>
+    <t>10082026-43</t>
+  </si>
+  <si>
+    <t>10082026-44</t>
+  </si>
+  <si>
+    <t>10082026-45</t>
+  </si>
+  <si>
+    <t>10082026-46</t>
+  </si>
+  <si>
+    <t>10082026-47</t>
+  </si>
+  <si>
+    <t>10082026-48</t>
+  </si>
+  <si>
+    <t>10082026-49</t>
+  </si>
+  <si>
+    <t>10082026-50</t>
+  </si>
+  <si>
+    <t>25-08-2026</t>
+  </si>
+  <si>
+    <t>Inclusive</t>
+  </si>
+  <si>
+    <t>After Tax</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>At Line Item Level</t>
   </si>
   <si>
     <t>SAVE AND APPROVE</t>
   </si>
   <si>
-    <t>Pear</t>
+    <t>SAVE AS DRAFT</t>
+  </si>
+  <si>
+    <t>None taxable item</t>
+  </si>
+  <si>
+    <t>Non inv 1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,6 +340,13 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -188,15 +384,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -222,10 +415,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -530,15 +733,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.28515625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" style="6" customWidth="1"/>
     <col min="2" max="2" width="24.42578125" customWidth="1"/>
     <col min="3" max="3" width="21.42578125" style="2" customWidth="1"/>
     <col min="4" max="4" width="16.28515625" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="5" customWidth="1"/>
     <col min="7" max="8" width="25.7109375" customWidth="1"/>
     <col min="9" max="9" width="17.28515625" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
@@ -550,156 +753,1692 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>6</v>
+      <c r="A1" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="10" t="s">
+      <c r="G1" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="L1" s="10" t="s">
+      <c r="M1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="10" t="s">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2">
+        <v>10</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="7" t="s">
+      <c r="M2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" s="6"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="G3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N3" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="7" t="s">
+      <c r="O3" s="6"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" t="s">
+        <v>89</v>
+      </c>
+      <c r="J4">
+        <v>10</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="M4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="N2" s="11" t="s">
+      <c r="N4" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="O4" s="6"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="O2" s="7"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="7"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="11"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="11"/>
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I5" t="s">
+        <v>89</v>
+      </c>
+      <c r="J5">
+        <v>10</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="11"/>
+      <c r="A6" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6">
+        <v>10</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="10" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="11"/>
+      <c r="A7" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7">
+        <v>10</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8">
+        <v>10</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" t="s">
+        <v>89</v>
+      </c>
+      <c r="J9">
+        <v>10</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I10" t="s">
+        <v>89</v>
+      </c>
+      <c r="J10">
+        <v>10</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N10" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11">
+        <v>10</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N11" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12">
+        <v>10</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N12" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13">
+        <v>10</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N13" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" t="s">
+        <v>89</v>
+      </c>
+      <c r="J14">
+        <v>10</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N14" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I15" t="s">
+        <v>89</v>
+      </c>
+      <c r="J15">
+        <v>10</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N15" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16">
+        <v>10</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N16" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17">
+        <v>10</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N17" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18">
+        <v>10</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N18" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19" t="s">
+        <v>89</v>
+      </c>
+      <c r="J19">
+        <v>10</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N19" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I20" t="s">
+        <v>89</v>
+      </c>
+      <c r="J20">
+        <v>10</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N20" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21">
+        <v>10</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N21" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22">
+        <v>10</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N22" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I23" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23">
+        <v>10</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" t="s">
+        <v>58</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24" t="s">
+        <v>89</v>
+      </c>
+      <c r="J24">
+        <v>10</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N24" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I25" t="s">
+        <v>89</v>
+      </c>
+      <c r="J25">
+        <v>10</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N25" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" t="s">
+        <v>60</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J26">
+        <v>10</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N26" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" t="s">
+        <v>61</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27">
+        <v>10</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N27" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" t="s">
+        <v>62</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28">
+        <v>10</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N28" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" t="s">
+        <v>63</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29" t="s">
+        <v>89</v>
+      </c>
+      <c r="J29">
+        <v>10</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N29" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" t="s">
+        <v>64</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I30" t="s">
+        <v>89</v>
+      </c>
+      <c r="J30">
+        <v>10</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N30" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" t="s">
+        <v>65</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31" t="s">
+        <v>18</v>
+      </c>
+      <c r="J31">
+        <v>10</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N31" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" t="s">
+        <v>66</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H32" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J32" s="18">
+        <v>10</v>
+      </c>
+      <c r="K32" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N32" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" t="s">
+        <v>67</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H33" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I33" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J33" s="18">
+        <v>10</v>
+      </c>
+      <c r="K33" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N33" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" t="s">
+        <v>68</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F34" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H34" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I34" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="J34" s="18">
+        <v>10</v>
+      </c>
+      <c r="K34" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N34" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H35" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I35" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="J35" s="18">
+        <v>10</v>
+      </c>
+      <c r="K35" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N35" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" t="s">
+        <v>70</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F36" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="H36" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I36" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" s="18">
+        <v>10</v>
+      </c>
+      <c r="K36" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N36" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" t="s">
+        <v>71</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F37" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G37" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H37" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I37" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J37" s="18">
+        <v>10</v>
+      </c>
+      <c r="K37" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N37" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B38" t="s">
+        <v>72</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G38" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H38" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I38" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J38" s="18">
+        <v>10</v>
+      </c>
+      <c r="K38" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N38" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" t="s">
+        <v>73</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F39" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G39" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H39" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I39" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="J39" s="18">
+        <v>10</v>
+      </c>
+      <c r="K39" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N39" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" t="s">
+        <v>74</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G40" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H40" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I40" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="J40" s="18">
+        <v>10</v>
+      </c>
+      <c r="K40" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N40" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41" t="s">
+        <v>75</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G41" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="H41" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I41" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J41" s="18">
+        <v>10</v>
+      </c>
+      <c r="K41" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N41" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" t="s">
+        <v>76</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H42" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="18">
+        <v>10</v>
+      </c>
+      <c r="K42" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N42" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B43" t="s">
+        <v>77</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F43" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H43" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I43" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J43" s="18">
+        <v>10</v>
+      </c>
+      <c r="K43" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N43" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" t="s">
+        <v>78</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F44" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H44" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I44" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="J44" s="18">
+        <v>10</v>
+      </c>
+      <c r="K44" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N44" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B45" t="s">
+        <v>79</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H45" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I45" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="J45" s="18">
+        <v>10</v>
+      </c>
+      <c r="K45" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N45" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B46" t="s">
+        <v>80</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F46" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="H46" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I46" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J46" s="18">
+        <v>10</v>
+      </c>
+      <c r="K46" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N46" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B47" t="s">
+        <v>81</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F47" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G47" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H47" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J47" s="18">
+        <v>10</v>
+      </c>
+      <c r="K47" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N47" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B48" t="s">
+        <v>82</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F48" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G48" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H48" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I48" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J48" s="18">
+        <v>10</v>
+      </c>
+      <c r="K48" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N48" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B49" t="s">
+        <v>83</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F49" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G49" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H49" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I49" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="J49" s="18">
+        <v>10</v>
+      </c>
+      <c r="K49" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N49" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B50" t="s">
+        <v>84</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F50" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G50" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H50" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I50" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="J50" s="18">
+        <v>10</v>
+      </c>
+      <c r="K50" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N50" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B51" t="s">
+        <v>85</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F51" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G51" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="H51" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I51" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J51" s="18">
+        <v>10</v>
+      </c>
+      <c r="K51" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N51" s="10" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -709,150 +2448,417 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="2" max="2" width="26.7109375" customWidth="1"/>
     <col min="3" max="3" width="13.85546875" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="14" t="s">
+    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="14" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="16">
-        <v>50</v>
-      </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
+      <c r="C2" s="15">
+        <v>5</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="15">
+        <v>10</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
+      <c r="A3" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="15">
+        <v>5</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="15">
+        <v>10</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
+      <c r="A4" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="15">
+        <v>5</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="15">
+        <v>10</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
+      <c r="A5" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="15">
+        <v>5</v>
+      </c>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
+      <c r="A6" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="15">
+        <v>5</v>
+      </c>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
+      <c r="A7" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="15">
+        <v>5</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="15">
+        <v>10</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
+      <c r="A8" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="15">
+        <v>5</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="15">
+        <v>10</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
+      <c r="A9" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="15">
+        <v>5</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="15">
+        <v>10</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
+      <c r="A10" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="15">
+        <v>5</v>
+      </c>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
+      <c r="A11" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="15">
+        <v>5</v>
+      </c>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="18"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
+      <c r="A12" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="15">
+        <v>5</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="15">
+        <v>10</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="18"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
+      <c r="A13" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="15">
+        <v>5</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="15">
+        <v>10</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="18"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
+      <c r="A14" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="15">
+        <v>5</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="15">
+        <v>10</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="18"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
+      <c r="A15" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="15">
+        <v>5</v>
+      </c>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="18"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
+      <c r="A16" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="15">
+        <v>5</v>
+      </c>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="18"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
+      <c r="A17" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="15">
+        <v>5</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="15">
+        <v>5</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="15">
+        <v>5</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" s="15">
+        <v>5</v>
+      </c>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="15">
+        <v>5</v>
+      </c>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="15">
+        <v>5</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="15">
+        <v>5</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="15">
+        <v>5</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" s="15">
+        <v>5</v>
+      </c>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="19">
+        <v>5</v>
+      </c>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
